--- a/ig/DM-MARS-2026/ValueSet-JDV-J222-NiveauConfidentialite-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J222-NiveauConfidentialite-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20220826120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,19 +102,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>Accès libre</t>
+    <t>Visible du grand public</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Accès restreint</t>
+    <t>Visible par les professionnels</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Accès très restreint</t>
+    <t>Visible régulation et gestion de crise</t>
   </si>
   <si>
     <t/>
